--- a/data/trans_orig/IP35_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP35_2023-Provincia-trans_orig.xlsx
@@ -848,7 +848,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4696</t>
+          <t>3730</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4133</t>
+          <t>4162</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>426</t>
+          <t>411</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>5029</t>
+          <t>5467</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,58%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2072</t>
+          <t>1915</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9105</t>
+          <t>9525</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6639</t>
+          <t>6359</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>19194</t>
+          <t>17847</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>9808</t>
+          <t>9827</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>22638</t>
+          <t>23925</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>15,67%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8183</t>
+          <t>8457</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20595</t>
+          <t>19687</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>26,87%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5423</t>
+          <t>5460</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17339</t>
+          <t>16585</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>20,9%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>16089</t>
+          <t>15856</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>31974</t>
+          <t>32812</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>21,5%</t>
         </is>
       </c>
     </row>
@@ -1222,7 +1222,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>6673</t>
+          <t>6500</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>7633</t>
+          <t>8712</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,71%</t>
         </is>
       </c>
     </row>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3277</t>
+          <t>3774</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1350,7 +1350,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>3165</t>
+          <t>3061</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1385,7 +1385,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,01%</t>
         </is>
       </c>
     </row>
@@ -1408,12 +1408,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5579</t>
+          <t>6010</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17850</t>
+          <t>18007</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1443,12 +1443,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1323</t>
+          <t>1264</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10023</t>
+          <t>10062</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1458,12 +1458,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1478,12 +1478,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8751</t>
+          <t>8143</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>22477</t>
+          <t>22182</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1493,12 +1493,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>14,53%</t>
         </is>
       </c>
     </row>
@@ -1521,12 +1521,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5582</t>
+          <t>5898</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>15407</t>
+          <t>15337</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1536,12 +1536,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1556,12 +1556,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3502</t>
+          <t>4205</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>12510</t>
+          <t>13177</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1571,12 +1571,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1591,12 +1591,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>11560</t>
+          <t>11212</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>24581</t>
+          <t>24410</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1606,12 +1606,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>15,99%</t>
         </is>
       </c>
     </row>
@@ -1634,12 +1634,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>538</t>
+          <t>477</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4800</t>
+          <t>4588</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1649,12 +1649,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1669,12 +1669,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>414</t>
+          <t>412</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4893</t>
+          <t>4745</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1689,7 +1689,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1421</t>
+          <t>1465</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>7257</t>
+          <t>7175</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1719,12 +1719,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,7%</t>
         </is>
       </c>
     </row>
@@ -1747,12 +1747,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7294</t>
+          <t>6970</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>22768</t>
+          <t>22254</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1762,12 +1762,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,07%</t>
+          <t>30,37%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1782,12 +1782,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11430</t>
+          <t>11158</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>24738</t>
+          <t>24775</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,17%</t>
+          <t>31,22%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1817,12 +1817,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>21433</t>
+          <t>21192</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>41143</t>
+          <t>41023</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>26,87%</t>
         </is>
       </c>
     </row>
@@ -1860,12 +1860,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3202</t>
+          <t>3345</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>12130</t>
+          <t>12240</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1875,12 +1875,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1895,12 +1895,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>8955</t>
+          <t>9244</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>22820</t>
+          <t>23012</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>28,75%</t>
+          <t>28,99%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1930,12 +1930,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>14794</t>
+          <t>14708</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>31149</t>
+          <t>31892</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>20,89%</t>
         </is>
       </c>
     </row>
@@ -1973,12 +1973,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4415</t>
+          <t>4463</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>28401</t>
+          <t>29156</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1988,12 +1988,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>38,76%</t>
+          <t>39,79%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2008,12 +2008,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>5475</t>
+          <t>5568</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>16240</t>
+          <t>16165</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2023,12 +2023,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>20,37%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2043,12 +2043,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>13602</t>
+          <t>13328</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>43475</t>
+          <t>40305</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2058,12 +2058,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>28,48%</t>
+          <t>26,4%</t>
         </is>
       </c>
     </row>
@@ -2126,7 +2126,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3832</t>
+          <t>3442</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3822</t>
+          <t>4185</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,74%</t>
         </is>
       </c>
     </row>
@@ -2434,7 +2434,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3250</t>
+          <t>3165</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2449,7 +2449,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>2232</t>
+          <t>2737</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2519,7 +2519,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>1,07%</t>
         </is>
       </c>
     </row>
@@ -2547,7 +2547,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4383</t>
+          <t>3763</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>3593</t>
+          <t>3301</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2632,7 +2632,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,29%</t>
         </is>
       </c>
     </row>
@@ -2655,12 +2655,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4833</t>
+          <t>4570</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>18370</t>
+          <t>18033</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2670,12 +2670,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,13%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2690,12 +2690,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>4011</t>
+          <t>4024</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>16861</t>
+          <t>16265</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2725,12 +2725,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>11145</t>
+          <t>11215</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>28945</t>
+          <t>29529</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,57%</t>
         </is>
       </c>
     </row>
@@ -2768,12 +2768,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1905</t>
+          <t>2257</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>11795</t>
+          <t>12120</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2783,12 +2783,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>7022</t>
+          <t>7235</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>19911</t>
+          <t>19216</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>11117</t>
+          <t>11063</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>27362</t>
+          <t>27161</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,64%</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>6104</t>
+          <t>4566</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2956,7 +2956,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4897</t>
+          <t>5919</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,32%</t>
         </is>
       </c>
     </row>
@@ -3107,12 +3107,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2494</t>
+          <t>2323</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>12460</t>
+          <t>12221</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3122,12 +3122,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3142,12 +3142,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>5468</t>
+          <t>5867</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>23654</t>
+          <t>26535</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3157,12 +3157,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>20,8%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3177,12 +3177,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>10717</t>
+          <t>9803</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>33037</t>
+          <t>30919</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>12,11%</t>
         </is>
       </c>
     </row>
@@ -3220,12 +3220,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>10403</t>
+          <t>9595</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>31343</t>
+          <t>31300</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3235,12 +3235,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>24,52%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3255,12 +3255,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>11238</t>
+          <t>11947</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>26850</t>
+          <t>27351</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3270,12 +3270,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3290,12 +3290,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>26341</t>
+          <t>26959</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>53940</t>
+          <t>53654</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3305,12 +3305,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>21,02%</t>
         </is>
       </c>
     </row>
@@ -3333,12 +3333,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>6261</t>
+          <t>5823</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>21562</t>
+          <t>23481</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3348,12 +3348,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3368,12 +3368,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>14081</t>
+          <t>13533</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>29028</t>
+          <t>29413</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>22547</t>
+          <t>23084</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>46734</t>
+          <t>46530</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>18,23%</t>
         </is>
       </c>
     </row>
@@ -3446,12 +3446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>12284</t>
+          <t>13100</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>85502</t>
+          <t>88714</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3461,12 +3461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>66,98%</t>
+          <t>69,5%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>8353</t>
+          <t>8610</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>21067</t>
+          <t>20693</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>25820</t>
+          <t>25011</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>126625</t>
+          <t>118470</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>49,61%</t>
+          <t>46,41%</t>
         </is>
       </c>
     </row>
@@ -3559,12 +3559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>8995</t>
+          <t>8698</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>28034</t>
+          <t>27511</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3574,12 +3574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>21,55%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>21138</t>
+          <t>20905</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>47013</t>
+          <t>45111</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3609,12 +3609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>36,85%</t>
+          <t>35,35%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3629,12 +3629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>30978</t>
+          <t>33316</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>66471</t>
+          <t>66968</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3644,12 +3644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>26,04%</t>
+          <t>26,24%</t>
         </is>
       </c>
     </row>
@@ -3672,12 +3672,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2112</t>
+          <t>2424</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>19337</t>
+          <t>18837</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3687,12 +3687,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3707,12 +3707,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3960</t>
+          <t>4508</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>15622</t>
+          <t>16582</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3722,12 +3722,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>8784</t>
+          <t>8934</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>27851</t>
+          <t>28296</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3757,12 +3757,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>11,09%</t>
         </is>
       </c>
     </row>
@@ -3790,7 +3790,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>4884</t>
+          <t>5049</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3805,7 +3805,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3825,7 +3825,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>7108</t>
+          <t>5984</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3855,12 +3855,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>465</t>
+          <t>821</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>6787</t>
+          <t>7039</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,76%</t>
         </is>
       </c>
     </row>
@@ -3903,7 +3903,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>5272</t>
+          <t>4544</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3918,7 +3918,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3938,7 +3938,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>3110</t>
+          <t>3538</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3953,7 +3953,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3968,12 +3968,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>460</t>
+          <t>494</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>5812</t>
+          <t>5402</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3983,12 +3983,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,12%</t>
         </is>
       </c>
     </row>
@@ -4354,12 +4354,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>3195</t>
+          <t>3287</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>11277</t>
+          <t>11063</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4369,12 +4369,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>4365</t>
+          <t>4232</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>13795</t>
+          <t>13923</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4404,12 +4404,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>20,73%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>9364</t>
+          <t>9309</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>21704</t>
+          <t>21001</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4439,12 +4439,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>16,74%</t>
         </is>
       </c>
     </row>
@@ -4467,12 +4467,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>1021</t>
+          <t>1082</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>6468</t>
+          <t>6200</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4507,7 +4507,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>3805</t>
+          <t>3241</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4522,7 +4522,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>1604</t>
+          <t>1558</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>7313</t>
+          <t>8096</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4552,12 +4552,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>6,45%</t>
         </is>
       </c>
     </row>
@@ -4806,12 +4806,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>3613</t>
+          <t>3570</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>11026</t>
+          <t>11233</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4821,12 +4821,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>19,28%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>3929</t>
+          <t>4083</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>13394</t>
+          <t>13102</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4856,12 +4856,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>9592</t>
+          <t>9366</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>21770</t>
+          <t>20549</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4891,12 +4891,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>16,38%</t>
         </is>
       </c>
     </row>
@@ -4919,12 +4919,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>2259</t>
+          <t>2444</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>9316</t>
+          <t>9217</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4934,12 +4934,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4954,12 +4954,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>2923</t>
+          <t>2907</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>11170</t>
+          <t>10853</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4969,12 +4969,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -4989,12 +4989,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>6257</t>
+          <t>6809</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>16635</t>
+          <t>16840</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,43%</t>
         </is>
       </c>
     </row>
@@ -5032,12 +5032,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>5458</t>
+          <t>5460</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>14429</t>
+          <t>14109</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5052,7 +5052,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>24,76%</t>
+          <t>24,21%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5067,12 +5067,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>8152</t>
+          <t>8580</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>18269</t>
+          <t>18686</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5082,12 +5082,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>27,2%</t>
+          <t>27,82%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5102,12 +5102,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>15905</t>
+          <t>16048</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>29417</t>
+          <t>29562</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>23,57%</t>
         </is>
       </c>
     </row>
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>6030</t>
+          <t>6305</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>15381</t>
+          <t>15733</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5160,12 +5160,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>26,4%</t>
+          <t>27,0%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5180,12 +5180,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>5277</t>
+          <t>5627</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>14668</t>
+          <t>14495</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5195,12 +5195,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>21,58%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5215,12 +5215,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>13132</t>
+          <t>13461</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>26353</t>
+          <t>25760</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5230,12 +5230,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>20,54%</t>
         </is>
       </c>
     </row>
@@ -5258,12 +5258,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>9749</t>
+          <t>10178</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>20410</t>
+          <t>20369</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5273,12 +5273,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>35,03%</t>
+          <t>34,96%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5293,12 +5293,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>11828</t>
+          <t>12380</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>23987</t>
+          <t>23711</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5308,12 +5308,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>35,71%</t>
+          <t>35,3%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>24374</t>
+          <t>24587</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>40056</t>
+          <t>39290</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5343,12 +5343,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>31,94%</t>
+          <t>31,32%</t>
         </is>
       </c>
     </row>
@@ -5371,12 +5371,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>546</t>
+          <t>552</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>5009</t>
+          <t>4835</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5386,12 +5386,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5406,12 +5406,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>1613</t>
+          <t>1726</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>7784</t>
+          <t>7598</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5421,12 +5421,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>2808</t>
+          <t>2782</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>9762</t>
+          <t>10106</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5456,12 +5456,12 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>8,06%</t>
         </is>
       </c>
     </row>
@@ -5489,7 +5489,7 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>3930</t>
+          <t>4374</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5504,7 +5504,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5519,12 +5519,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>456</t>
+          <t>661</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>5402</t>
+          <t>5401</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5534,7 +5534,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>1279</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>7062</t>
+          <t>7295</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5569,12 +5569,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,82%</t>
         </is>
       </c>
     </row>
@@ -5980,7 +5980,7 @@
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>4698</t>
+          <t>4955</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -5995,7 +5995,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6015,7 +6015,7 @@
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>4693</t>
+          <t>4164</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6030,7 +6030,7 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>2,81%</t>
         </is>
       </c>
     </row>
@@ -6053,12 +6053,12 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>13533</t>
+          <t>13656</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>26677</t>
+          <t>26766</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>38,03%</t>
+          <t>38,16%</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>10040</t>
+          <t>9543</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>28331</t>
+          <t>27035</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6103,12 +6103,12 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>36,26%</t>
+          <t>34,6%</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6123,12 +6123,12 @@
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>26930</t>
+          <t>26379</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>50408</t>
+          <t>49567</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -6138,12 +6138,12 @@
       </c>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>34,0%</t>
+          <t>33,43%</t>
         </is>
       </c>
     </row>
@@ -6166,12 +6166,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>4339</t>
+          <t>4011</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>13527</t>
+          <t>13519</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>19,27%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>3241</t>
+          <t>3266</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>14305</t>
+          <t>14189</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6216,12 +6216,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6236,12 +6236,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>9320</t>
+          <t>8970</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>22868</t>
+          <t>23333</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -6251,12 +6251,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>15,74%</t>
         </is>
       </c>
     </row>
@@ -6284,7 +6284,7 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>2558</t>
+          <t>2276</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6299,7 +6299,7 @@
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6354,7 +6354,7 @@
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>2747</t>
+          <t>2414</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -6369,7 +6369,7 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,63%</t>
         </is>
       </c>
     </row>
@@ -6432,7 +6432,7 @@
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>2772</t>
+          <t>2464</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6447,7 +6447,7 @@
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6467,7 +6467,7 @@
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>2993</t>
+          <t>2502</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -6482,7 +6482,7 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,69%</t>
         </is>
       </c>
     </row>
@@ -6505,12 +6505,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>6455</t>
+          <t>6773</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>18527</t>
+          <t>17792</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6520,12 +6520,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>26,41%</t>
+          <t>25,37%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6540,12 +6540,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>3313</t>
+          <t>3062</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>15085</t>
+          <t>13966</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6555,12 +6555,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6575,12 +6575,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>11715</t>
+          <t>11563</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>27852</t>
+          <t>27744</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -6590,12 +6590,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>18,71%</t>
         </is>
       </c>
     </row>
@@ -6618,12 +6618,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>1341</t>
+          <t>1384</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>8934</t>
+          <t>8356</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -6633,12 +6633,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6653,12 +6653,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>1703</t>
+          <t>1784</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>12837</t>
+          <t>11185</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -6668,12 +6668,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6688,12 +6688,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>4158</t>
+          <t>4148</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>16365</t>
+          <t>16207</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -6708,7 +6708,7 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>10,93%</t>
         </is>
       </c>
     </row>
@@ -6736,7 +6736,7 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>4710</t>
+          <t>3908</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -6751,7 +6751,7 @@
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>11782</t>
+          <t>9717</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -6786,7 +6786,7 @@
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -6801,12 +6801,12 @@
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>595</t>
+          <t>599</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>9251</t>
+          <t>9938</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
@@ -6821,7 +6821,7 @@
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,7%</t>
         </is>
       </c>
     </row>
@@ -6844,12 +6844,12 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>4776</t>
+          <t>4504</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>15335</t>
+          <t>14805</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -6859,12 +6859,12 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -6879,12 +6879,12 @@
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>8110</t>
+          <t>8083</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>44094</t>
+          <t>43784</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>56,43%</t>
+          <t>56,04%</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -6914,12 +6914,12 @@
       </c>
       <c r="S58" s="2" t="inlineStr">
         <is>
-          <t>15842</t>
+          <t>16956</t>
         </is>
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>56228</t>
+          <t>63521</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
@@ -6929,12 +6929,12 @@
       </c>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>37,92%</t>
+          <t>42,84%</t>
         </is>
       </c>
     </row>
@@ -6957,12 +6957,12 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>8666</t>
+          <t>8472</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>21709</t>
+          <t>21826</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -6972,12 +6972,12 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>30,95%</t>
+          <t>31,12%</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
@@ -6992,12 +6992,12 @@
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>6127</t>
+          <t>6223</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>23882</t>
+          <t>23823</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -7007,12 +7007,12 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>30,49%</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7027,12 +7027,12 @@
       </c>
       <c r="S59" s="2" t="inlineStr">
         <is>
-          <t>18380</t>
+          <t>19142</t>
         </is>
       </c>
       <c r="T59" s="2" t="inlineStr">
         <is>
-          <t>40951</t>
+          <t>41927</t>
         </is>
       </c>
       <c r="U59" s="2" t="inlineStr">
@@ -7042,12 +7042,12 @@
       </c>
       <c r="V59" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>27,62%</t>
+          <t>28,28%</t>
         </is>
       </c>
     </row>
@@ -7070,12 +7070,12 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>520</t>
+          <t>524</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>5760</t>
+          <t>6225</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -7085,12 +7085,12 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>7925</t>
+          <t>8284</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -7125,7 +7125,7 @@
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7140,12 +7140,12 @@
       </c>
       <c r="S60" s="2" t="inlineStr">
         <is>
-          <t>890</t>
+          <t>900</t>
         </is>
       </c>
       <c r="T60" s="2" t="inlineStr">
         <is>
-          <t>9769</t>
+          <t>9273</t>
         </is>
       </c>
       <c r="U60" s="2" t="inlineStr">
@@ -7155,12 +7155,12 @@
       </c>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,25%</t>
         </is>
       </c>
     </row>
@@ -7188,7 +7188,7 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>3573</t>
+          <t>3082</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -7203,7 +7203,7 @@
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
@@ -7223,7 +7223,7 @@
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>3269</t>
+          <t>2983</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -7238,7 +7238,7 @@
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7253,12 +7253,12 @@
       </c>
       <c r="S61" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>422</t>
         </is>
       </c>
       <c r="T61" s="2" t="inlineStr">
         <is>
-          <t>4172</t>
+          <t>4256</t>
         </is>
       </c>
       <c r="U61" s="2" t="inlineStr">
@@ -7268,12 +7268,12 @@
       </c>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,87%</t>
         </is>
       </c>
     </row>
@@ -7752,12 +7752,12 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>474</t>
+          <t>472</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>4435</t>
+          <t>4364</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -7772,7 +7772,7 @@
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
@@ -7792,7 +7792,7 @@
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>2765</t>
+          <t>3166</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -7807,7 +7807,7 @@
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="S66" s="2" t="inlineStr">
         <is>
-          <t>616</t>
+          <t>571</t>
         </is>
       </c>
       <c r="T66" s="2" t="inlineStr">
         <is>
-          <t>5240</t>
+          <t>5436</t>
         </is>
       </c>
       <c r="U66" s="2" t="inlineStr">
@@ -7837,12 +7837,12 @@
       </c>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>7,23%</t>
         </is>
       </c>
     </row>
@@ -7865,12 +7865,12 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>2515</t>
+          <t>2623</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>8267</t>
+          <t>8396</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>24,33%</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
@@ -7900,12 +7900,12 @@
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>4881</t>
+          <t>4786</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>13408</t>
+          <t>13636</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -7915,12 +7915,12 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>33,49%</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -7935,12 +7935,12 @@
       </c>
       <c r="S67" s="2" t="inlineStr">
         <is>
-          <t>8675</t>
+          <t>9106</t>
         </is>
       </c>
       <c r="T67" s="2" t="inlineStr">
         <is>
-          <t>18886</t>
+          <t>18562</t>
         </is>
       </c>
       <c r="U67" s="2" t="inlineStr">
@@ -7950,12 +7950,12 @@
       </c>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>24,67%</t>
         </is>
       </c>
     </row>
@@ -7978,12 +7978,12 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>3286</t>
+          <t>3488</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>9039</t>
+          <t>9436</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -7993,12 +7993,12 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>26,19%</t>
+          <t>27,34%</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
@@ -8013,12 +8013,12 @@
       </c>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>3203</t>
+          <t>3099</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>10179</t>
+          <t>10197</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -8028,12 +8028,12 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>25,04%</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -8048,12 +8048,12 @@
       </c>
       <c r="S68" s="2" t="inlineStr">
         <is>
-          <t>7319</t>
+          <t>7467</t>
         </is>
       </c>
       <c r="T68" s="2" t="inlineStr">
         <is>
-          <t>16971</t>
+          <t>16449</t>
         </is>
       </c>
       <c r="U68" s="2" t="inlineStr">
@@ -8063,12 +8063,12 @@
       </c>
       <c r="V68" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>21,87%</t>
         </is>
       </c>
     </row>
@@ -8096,7 +8096,7 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>2442</t>
+          <t>2380</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
@@ -8111,7 +8111,7 @@
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
@@ -8126,12 +8126,12 @@
       </c>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>1363</t>
+          <t>1178</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>6599</t>
+          <t>6655</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -8141,12 +8141,12 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -8161,12 +8161,12 @@
       </c>
       <c r="S69" s="2" t="inlineStr">
         <is>
-          <t>1619</t>
+          <t>1622</t>
         </is>
       </c>
       <c r="T69" s="2" t="inlineStr">
         <is>
-          <t>7877</t>
+          <t>7240</t>
         </is>
       </c>
       <c r="U69" s="2" t="inlineStr">
@@ -8176,12 +8176,12 @@
       </c>
       <c r="V69" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>9,62%</t>
         </is>
       </c>
     </row>
@@ -8204,12 +8204,12 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>1802</t>
+          <t>1752</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>7234</t>
+          <t>7442</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
@@ -8219,12 +8219,12 @@
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
@@ -8239,12 +8239,12 @@
       </c>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>2563</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>9235</t>
+          <t>9168</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>22,52%</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
@@ -8274,12 +8274,12 @@
       </c>
       <c r="S70" s="2" t="inlineStr">
         <is>
-          <t>5632</t>
+          <t>5730</t>
         </is>
       </c>
       <c r="T70" s="2" t="inlineStr">
         <is>
-          <t>14407</t>
+          <t>14217</t>
         </is>
       </c>
       <c r="U70" s="2" t="inlineStr">
@@ -8289,12 +8289,12 @@
       </c>
       <c r="V70" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>18,9%</t>
         </is>
       </c>
     </row>
@@ -8317,12 +8317,12 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>2537</t>
+          <t>2599</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>8714</t>
+          <t>8745</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
@@ -8332,12 +8332,12 @@
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>25,34%</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
@@ -8352,12 +8352,12 @@
       </c>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>1156</t>
+          <t>1131</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>5712</t>
+          <t>5971</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -8367,12 +8367,12 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -8387,12 +8387,12 @@
       </c>
       <c r="S71" s="2" t="inlineStr">
         <is>
-          <t>4350</t>
+          <t>4616</t>
         </is>
       </c>
       <c r="T71" s="2" t="inlineStr">
         <is>
-          <t>12682</t>
+          <t>12866</t>
         </is>
       </c>
       <c r="U71" s="2" t="inlineStr">
@@ -8402,12 +8402,12 @@
       </c>
       <c r="V71" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="W71" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>17,1%</t>
         </is>
       </c>
     </row>
@@ -8430,12 +8430,12 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>366</t>
+          <t>369</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>3901</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
@@ -8445,12 +8445,12 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
@@ -8465,12 +8465,12 @@
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>337</t>
+          <t>339</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>4275</t>
+          <t>4357</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -8485,7 +8485,7 @@
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
@@ -8500,12 +8500,12 @@
       </c>
       <c r="S72" s="2" t="inlineStr">
         <is>
-          <t>1187</t>
+          <t>1086</t>
         </is>
       </c>
       <c r="T72" s="2" t="inlineStr">
         <is>
-          <t>6500</t>
+          <t>6186</t>
         </is>
       </c>
       <c r="U72" s="2" t="inlineStr">
@@ -8515,12 +8515,12 @@
       </c>
       <c r="V72" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="W72" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,22%</t>
         </is>
       </c>
     </row>
@@ -8543,12 +8543,12 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>4576</t>
+          <t>4663</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>11502</t>
+          <t>11441</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
@@ -8558,12 +8558,12 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>33,33%</t>
+          <t>33,15%</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
@@ -8578,12 +8578,12 @@
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>2497</t>
+          <t>2276</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>8966</t>
+          <t>8551</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -8593,12 +8593,12 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>21,0%</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -8613,12 +8613,12 @@
       </c>
       <c r="S73" s="2" t="inlineStr">
         <is>
-          <t>8207</t>
+          <t>8337</t>
         </is>
       </c>
       <c r="T73" s="2" t="inlineStr">
         <is>
-          <t>17944</t>
+          <t>17488</t>
         </is>
       </c>
       <c r="U73" s="2" t="inlineStr">
@@ -8628,12 +8628,12 @@
       </c>
       <c r="V73" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>23,24%</t>
         </is>
       </c>
     </row>
@@ -8656,12 +8656,12 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>1109</t>
+          <t>1097</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>6163</t>
+          <t>5936</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
@@ -8671,12 +8671,12 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
@@ -8691,12 +8691,12 @@
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>3146</t>
+          <t>3259</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>12330</t>
+          <t>11565</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -8706,12 +8706,12 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>30,28%</t>
+          <t>28,4%</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -8726,12 +8726,12 @@
       </c>
       <c r="S74" s="2" t="inlineStr">
         <is>
-          <t>5419</t>
+          <t>5255</t>
         </is>
       </c>
       <c r="T74" s="2" t="inlineStr">
         <is>
-          <t>15303</t>
+          <t>14906</t>
         </is>
       </c>
       <c r="U74" s="2" t="inlineStr">
@@ -8741,12 +8741,12 @@
       </c>
       <c r="V74" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>19,81%</t>
         </is>
       </c>
     </row>
@@ -8774,7 +8774,7 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>3315</t>
+          <t>3623</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
@@ -8789,7 +8789,7 @@
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
@@ -8804,12 +8804,12 @@
       </c>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>550</t>
+          <t>547</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>5108</t>
+          <t>4744</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
@@ -8839,12 +8839,12 @@
       </c>
       <c r="S75" s="2" t="inlineStr">
         <is>
-          <t>951</t>
+          <t>1025</t>
         </is>
       </c>
       <c r="T75" s="2" t="inlineStr">
         <is>
-          <t>6214</t>
+          <t>6213</t>
         </is>
       </c>
       <c r="U75" s="2" t="inlineStr">
@@ -8854,7 +8854,7 @@
       </c>
       <c r="V75" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="W75" s="2" t="inlineStr">
@@ -9451,12 +9451,12 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>3603</t>
+          <t>4147</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>11657</t>
+          <t>11782</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
@@ -9466,12 +9466,12 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>25,52%</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
@@ -9486,12 +9486,12 @@
       </c>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>5924</t>
+          <t>5869</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>15050</t>
+          <t>14947</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -9501,12 +9501,12 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>26,79%</t>
+          <t>26,6%</t>
         </is>
       </c>
       <c r="Q81" s="2" t="inlineStr">
@@ -9521,12 +9521,12 @@
       </c>
       <c r="S81" s="2" t="inlineStr">
         <is>
-          <t>11495</t>
+          <t>11567</t>
         </is>
       </c>
       <c r="T81" s="2" t="inlineStr">
         <is>
-          <t>23980</t>
+          <t>23645</t>
         </is>
       </c>
       <c r="U81" s="2" t="inlineStr">
@@ -9536,12 +9536,12 @@
       </c>
       <c r="V81" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="W81" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>23,1%</t>
         </is>
       </c>
     </row>
@@ -9564,12 +9564,12 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>1347</t>
+          <t>1343</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>7231</t>
+          <t>7082</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
@@ -9579,12 +9579,12 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
@@ -9599,12 +9599,12 @@
       </c>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>367</t>
+          <t>347</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>4106</t>
+          <t>4645</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -9614,12 +9614,12 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="Q82" s="2" t="inlineStr">
@@ -9634,12 +9634,12 @@
       </c>
       <c r="S82" s="2" t="inlineStr">
         <is>
-          <t>2422</t>
+          <t>2305</t>
         </is>
       </c>
       <c r="T82" s="2" t="inlineStr">
         <is>
-          <t>9433</t>
+          <t>8852</t>
         </is>
       </c>
       <c r="U82" s="2" t="inlineStr">
@@ -9649,12 +9649,12 @@
       </c>
       <c r="V82" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="W82" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>8,65%</t>
         </is>
       </c>
     </row>
@@ -9903,12 +9903,12 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>3881</t>
+          <t>4151</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>11105</t>
+          <t>11422</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
@@ -9918,12 +9918,12 @@
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>24,74%</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr">
@@ -9938,12 +9938,12 @@
       </c>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>2957</t>
+          <t>3223</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>10177</t>
+          <t>10827</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
@@ -9953,12 +9953,12 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>19,27%</t>
         </is>
       </c>
       <c r="Q85" s="2" t="inlineStr">
@@ -9973,12 +9973,12 @@
       </c>
       <c r="S85" s="2" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>8500</t>
         </is>
       </c>
       <c r="T85" s="2" t="inlineStr">
         <is>
-          <t>19237</t>
+          <t>19075</t>
         </is>
       </c>
       <c r="U85" s="2" t="inlineStr">
@@ -9988,12 +9988,12 @@
       </c>
       <c r="V85" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="W85" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>18,64%</t>
         </is>
       </c>
     </row>
@@ -10016,12 +10016,12 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>1783</t>
+          <t>1829</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>8048</t>
+          <t>7806</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
@@ -10031,12 +10031,12 @@
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
@@ -10051,12 +10051,12 @@
       </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>1091</t>
+          <t>1308</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>7249</t>
+          <t>7168</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -10066,12 +10066,12 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="Q86" s="2" t="inlineStr">
@@ -10086,12 +10086,12 @@
       </c>
       <c r="S86" s="2" t="inlineStr">
         <is>
-          <t>4209</t>
+          <t>4038</t>
         </is>
       </c>
       <c r="T86" s="2" t="inlineStr">
         <is>
-          <t>12637</t>
+          <t>12693</t>
         </is>
       </c>
       <c r="U86" s="2" t="inlineStr">
@@ -10101,12 +10101,12 @@
       </c>
       <c r="V86" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="W86" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,4%</t>
         </is>
       </c>
     </row>
@@ -10129,12 +10129,12 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>1168</t>
+          <t>1162</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>6365</t>
+          <t>6379</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
@@ -10144,12 +10144,12 @@
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr">
@@ -10164,12 +10164,12 @@
       </c>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>5100</t>
+          <t>5355</t>
         </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>14375</t>
+          <t>14356</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
@@ -10179,12 +10179,12 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>25,55%</t>
         </is>
       </c>
       <c r="Q87" s="2" t="inlineStr">
@@ -10199,12 +10199,12 @@
       </c>
       <c r="S87" s="2" t="inlineStr">
         <is>
-          <t>7530</t>
+          <t>7507</t>
         </is>
       </c>
       <c r="T87" s="2" t="inlineStr">
         <is>
-          <t>18530</t>
+          <t>17969</t>
         </is>
       </c>
       <c r="U87" s="2" t="inlineStr">
@@ -10214,12 +10214,12 @@
       </c>
       <c r="V87" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="W87" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>17,56%</t>
         </is>
       </c>
     </row>
@@ -10242,12 +10242,12 @@
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>3028</t>
+          <t>3064</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>10134</t>
+          <t>9645</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
@@ -10257,12 +10257,12 @@
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr">
@@ -10277,12 +10277,12 @@
       </c>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>3935</t>
+          <t>4055</t>
         </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>11325</t>
+          <t>11819</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -10292,12 +10292,12 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="Q88" s="2" t="inlineStr">
@@ -10312,12 +10312,12 @@
       </c>
       <c r="S88" s="2" t="inlineStr">
         <is>
-          <t>8735</t>
+          <t>9079</t>
         </is>
       </c>
       <c r="T88" s="2" t="inlineStr">
         <is>
-          <t>19048</t>
+          <t>18799</t>
         </is>
       </c>
       <c r="U88" s="2" t="inlineStr">
@@ -10327,12 +10327,12 @@
       </c>
       <c r="V88" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="W88" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>18,37%</t>
         </is>
       </c>
     </row>
@@ -10355,12 +10355,12 @@
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>5426</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>14092</t>
+          <t>13768</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
@@ -10370,12 +10370,12 @@
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>30,52%</t>
+          <t>29,82%</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr">
@@ -10390,12 +10390,12 @@
       </c>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>7558</t>
+          <t>7508</t>
         </is>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>17259</t>
+          <t>17107</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
@@ -10405,12 +10405,12 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>30,45%</t>
         </is>
       </c>
       <c r="Q89" s="2" t="inlineStr">
@@ -10425,12 +10425,12 @@
       </c>
       <c r="S89" s="2" t="inlineStr">
         <is>
-          <t>15383</t>
+          <t>14953</t>
         </is>
       </c>
       <c r="T89" s="2" t="inlineStr">
         <is>
-          <t>28380</t>
+          <t>29109</t>
         </is>
       </c>
       <c r="U89" s="2" t="inlineStr">
@@ -10440,12 +10440,12 @@
       </c>
       <c r="V89" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="W89" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>28,44%</t>
         </is>
       </c>
     </row>
@@ -10468,12 +10468,12 @@
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>1052</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>6987</t>
+          <t>6975</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
@@ -10483,12 +10483,12 @@
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
@@ -10503,12 +10503,12 @@
       </c>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>1078</t>
+          <t>1158</t>
         </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>6508</t>
+          <t>6643</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -10518,12 +10518,12 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="Q90" s="2" t="inlineStr">
@@ -10538,12 +10538,12 @@
       </c>
       <c r="S90" s="2" t="inlineStr">
         <is>
-          <t>3481</t>
+          <t>3344</t>
         </is>
       </c>
       <c r="T90" s="2" t="inlineStr">
         <is>
-          <t>10872</t>
+          <t>11204</t>
         </is>
       </c>
       <c r="U90" s="2" t="inlineStr">
@@ -10553,12 +10553,12 @@
       </c>
       <c r="V90" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="W90" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,95%</t>
         </is>
       </c>
     </row>
@@ -10581,12 +10581,12 @@
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>568</t>
+          <t>731</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>5598</t>
+          <t>5762</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
@@ -10596,12 +10596,12 @@
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr">
@@ -10616,12 +10616,12 @@
       </c>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>654</t>
         </is>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>10757</t>
+          <t>10201</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
@@ -10631,12 +10631,12 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="Q91" s="2" t="inlineStr">
@@ -10651,12 +10651,12 @@
       </c>
       <c r="S91" s="2" t="inlineStr">
         <is>
-          <t>2112</t>
+          <t>2257</t>
         </is>
       </c>
       <c r="T91" s="2" t="inlineStr">
         <is>
-          <t>12658</t>
+          <t>12007</t>
         </is>
       </c>
       <c r="U91" s="2" t="inlineStr">
@@ -10666,12 +10666,12 @@
       </c>
       <c r="V91" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="W91" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>11,73%</t>
         </is>
       </c>
     </row>
@@ -10699,7 +10699,7 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>3471</t>
+          <t>3329</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
@@ -10714,7 +10714,7 @@
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
@@ -10734,7 +10734,7 @@
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>3845</t>
+          <t>4198</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
@@ -10749,7 +10749,7 @@
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="Q92" s="2" t="inlineStr">
@@ -10764,12 +10764,12 @@
       </c>
       <c r="S92" s="2" t="inlineStr">
         <is>
-          <t>593</t>
+          <t>677</t>
         </is>
       </c>
       <c r="T92" s="2" t="inlineStr">
         <is>
-          <t>5439</t>
+          <t>5226</t>
         </is>
       </c>
       <c r="U92" s="2" t="inlineStr">
@@ -10779,12 +10779,12 @@
       </c>
       <c r="V92" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W92" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,11%</t>
         </is>
       </c>
     </row>
@@ -10964,7 +10964,7 @@
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>4741</t>
+          <t>5591</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
@@ -10979,7 +10979,7 @@
       </c>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="Q94" s="2" t="inlineStr">
@@ -10999,7 +10999,7 @@
       </c>
       <c r="T94" s="2" t="inlineStr">
         <is>
-          <t>4469</t>
+          <t>4888</t>
         </is>
       </c>
       <c r="U94" s="2" t="inlineStr">
@@ -11014,7 +11014,7 @@
       </c>
       <c r="W94" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,75%</t>
         </is>
       </c>
     </row>
@@ -11042,7 +11042,7 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>3143</t>
+          <t>3154</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
@@ -11057,7 +11057,7 @@
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
@@ -11077,7 +11077,7 @@
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>4577</t>
+          <t>4301</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
@@ -11092,7 +11092,7 @@
       </c>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="Q95" s="2" t="inlineStr">
@@ -11107,12 +11107,12 @@
       </c>
       <c r="S95" s="2" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>163</t>
         </is>
       </c>
       <c r="T95" s="2" t="inlineStr">
         <is>
-          <t>5061</t>
+          <t>5055</t>
         </is>
       </c>
       <c r="U95" s="2" t="inlineStr">
@@ -11150,12 +11150,12 @@
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>16538</t>
+          <t>16492</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>31352</t>
+          <t>31869</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
@@ -11165,12 +11165,12 @@
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>25,47%</t>
+          <t>25,89%</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
@@ -11185,12 +11185,12 @@
       </c>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>22382</t>
+          <t>22959</t>
         </is>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>43825</t>
+          <t>44821</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
@@ -11200,12 +11200,12 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>28,73%</t>
         </is>
       </c>
       <c r="Q96" s="2" t="inlineStr">
@@ -11220,12 +11220,12 @@
       </c>
       <c r="S96" s="2" t="inlineStr">
         <is>
-          <t>43264</t>
+          <t>43070</t>
         </is>
       </c>
       <c r="T96" s="2" t="inlineStr">
         <is>
-          <t>68661</t>
+          <t>69122</t>
         </is>
       </c>
       <c r="U96" s="2" t="inlineStr">
@@ -11235,12 +11235,12 @@
       </c>
       <c r="V96" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="W96" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>24,77%</t>
         </is>
       </c>
     </row>
@@ -11263,12 +11263,12 @@
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>3330</t>
+          <t>3540</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>12231</t>
+          <t>13339</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
@@ -11278,12 +11278,12 @@
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr">
@@ -11298,12 +11298,12 @@
       </c>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>6195</t>
+          <t>6361</t>
         </is>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>20151</t>
+          <t>20154</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
@@ -11313,7 +11313,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11333,12 +11333,12 @@
       </c>
       <c r="S97" s="2" t="inlineStr">
         <is>
-          <t>11993</t>
+          <t>12013</t>
         </is>
       </c>
       <c r="T97" s="2" t="inlineStr">
         <is>
-          <t>28259</t>
+          <t>27927</t>
         </is>
       </c>
       <c r="U97" s="2" t="inlineStr">
@@ -11353,7 +11353,7 @@
       </c>
       <c r="W97" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,01%</t>
         </is>
       </c>
     </row>
@@ -11376,12 +11376,12 @@
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>1158</t>
+          <t>1027</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>7402</t>
+          <t>7256</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
@@ -11391,12 +11391,12 @@
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr">
@@ -11411,12 +11411,12 @@
       </c>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>1053</t>
+          <t>954</t>
         </is>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>8548</t>
+          <t>9096</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
@@ -11426,12 +11426,12 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="Q98" s="2" t="inlineStr">
@@ -11446,12 +11446,12 @@
       </c>
       <c r="S98" s="2" t="inlineStr">
         <is>
-          <t>3142</t>
+          <t>3160</t>
         </is>
       </c>
       <c r="T98" s="2" t="inlineStr">
         <is>
-          <t>12503</t>
+          <t>12957</t>
         </is>
       </c>
       <c r="U98" s="2" t="inlineStr">
@@ -11466,7 +11466,7 @@
       </c>
       <c r="W98" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,64%</t>
         </is>
       </c>
     </row>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>1951</t>
+          <t>1781</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
@@ -11509,7 +11509,7 @@
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr">
@@ -11564,7 +11564,7 @@
       </c>
       <c r="T99" s="2" t="inlineStr">
         <is>
-          <t>2041</t>
+          <t>2179</t>
         </is>
       </c>
       <c r="U99" s="2" t="inlineStr">
@@ -11579,7 +11579,7 @@
       </c>
       <c r="W99" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,78%</t>
         </is>
       </c>
     </row>
@@ -11602,12 +11602,12 @@
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>8673</t>
+          <t>8567</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>20403</t>
+          <t>20369</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
@@ -11617,12 +11617,12 @@
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr">
@@ -11637,12 +11637,12 @@
       </c>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>7242</t>
+          <t>7243</t>
         </is>
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>20886</t>
+          <t>20096</t>
         </is>
       </c>
       <c r="N100" s="2" t="inlineStr">
@@ -11657,7 +11657,7 @@
       </c>
       <c r="P100" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="Q100" s="2" t="inlineStr">
@@ -11672,12 +11672,12 @@
       </c>
       <c r="S100" s="2" t="inlineStr">
         <is>
-          <t>18625</t>
+          <t>18563</t>
         </is>
       </c>
       <c r="T100" s="2" t="inlineStr">
         <is>
-          <t>36463</t>
+          <t>36915</t>
         </is>
       </c>
       <c r="U100" s="2" t="inlineStr">
@@ -11687,12 +11687,12 @@
       </c>
       <c r="V100" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="W100" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>13,23%</t>
         </is>
       </c>
     </row>
@@ -11715,12 +11715,12 @@
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>12145</t>
+          <t>11462</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>29351</t>
+          <t>30440</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
@@ -11730,12 +11730,12 @@
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>24,73%</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr">
@@ -11750,12 +11750,12 @@
       </c>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>11863</t>
+          <t>11574</t>
         </is>
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>32372</t>
+          <t>32674</t>
         </is>
       </c>
       <c r="N101" s="2" t="inlineStr">
@@ -11765,12 +11765,12 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>20,94%</t>
         </is>
       </c>
       <c r="Q101" s="2" t="inlineStr">
@@ -11785,12 +11785,12 @@
       </c>
       <c r="S101" s="2" t="inlineStr">
         <is>
-          <t>26364</t>
+          <t>26217</t>
         </is>
       </c>
       <c r="T101" s="2" t="inlineStr">
         <is>
-          <t>54766</t>
+          <t>53882</t>
         </is>
       </c>
       <c r="U101" s="2" t="inlineStr">
@@ -11800,12 +11800,12 @@
       </c>
       <c r="V101" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="W101" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>19,31%</t>
         </is>
       </c>
     </row>
@@ -11828,12 +11828,12 @@
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>2195</t>
+          <t>2254</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>9796</t>
+          <t>10107</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
@@ -11843,12 +11843,12 @@
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr">
@@ -11863,12 +11863,12 @@
       </c>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>7272</t>
+          <t>7974</t>
         </is>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>20484</t>
+          <t>21221</t>
         </is>
       </c>
       <c r="N102" s="2" t="inlineStr">
@@ -11878,12 +11878,12 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="Q102" s="2" t="inlineStr">
@@ -11898,12 +11898,12 @@
       </c>
       <c r="S102" s="2" t="inlineStr">
         <is>
-          <t>12076</t>
+          <t>12027</t>
         </is>
       </c>
       <c r="T102" s="2" t="inlineStr">
         <is>
-          <t>26305</t>
+          <t>27353</t>
         </is>
       </c>
       <c r="U102" s="2" t="inlineStr">
@@ -11913,12 +11913,12 @@
       </c>
       <c r="V102" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="W102" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,8%</t>
         </is>
       </c>
     </row>
@@ -11941,12 +11941,12 @@
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>13941</t>
+          <t>14003</t>
         </is>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>28252</t>
+          <t>28056</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
@@ -11956,12 +11956,12 @@
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="J103" s="2" t="inlineStr">
@@ -11976,12 +11976,12 @@
       </c>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>11135</t>
+          <t>10630</t>
         </is>
       </c>
       <c r="M103" s="2" t="inlineStr">
         <is>
-          <t>37834</t>
+          <t>37339</t>
         </is>
       </c>
       <c r="N103" s="2" t="inlineStr">
@@ -11991,12 +11991,12 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
         <is>
-          <t>24,25%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="Q103" s="2" t="inlineStr">
@@ -12011,12 +12011,12 @@
       </c>
       <c r="S103" s="2" t="inlineStr">
         <is>
-          <t>28009</t>
+          <t>28093</t>
         </is>
       </c>
       <c r="T103" s="2" t="inlineStr">
         <is>
-          <t>56020</t>
+          <t>55672</t>
         </is>
       </c>
       <c r="U103" s="2" t="inlineStr">
@@ -12026,12 +12026,12 @@
       </c>
       <c r="V103" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="W103" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>19,95%</t>
         </is>
       </c>
     </row>
@@ -12054,12 +12054,12 @@
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>15004</t>
+          <t>15197</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>29522</t>
+          <t>29095</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
@@ -12069,12 +12069,12 @@
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>23,64%</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr">
@@ -12089,12 +12089,12 @@
       </c>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t>15308</t>
+          <t>16462</t>
         </is>
       </c>
       <c r="M104" s="2" t="inlineStr">
         <is>
-          <t>34550</t>
+          <t>33337</t>
         </is>
       </c>
       <c r="N104" s="2" t="inlineStr">
@@ -12104,12 +12104,12 @@
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>21,37%</t>
         </is>
       </c>
       <c r="Q104" s="2" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="S104" s="2" t="inlineStr">
         <is>
-          <t>35047</t>
+          <t>35540</t>
         </is>
       </c>
       <c r="T104" s="2" t="inlineStr">
         <is>
-          <t>57967</t>
+          <t>57683</t>
         </is>
       </c>
       <c r="U104" s="2" t="inlineStr">
@@ -12139,12 +12139,12 @@
       </c>
       <c r="V104" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="W104" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>20,67%</t>
         </is>
       </c>
     </row>
@@ -12167,12 +12167,12 @@
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>5914</t>
+          <t>5868</t>
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>16188</t>
+          <t>16462</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
@@ -12182,12 +12182,12 @@
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="J105" s="2" t="inlineStr">
@@ -12202,12 +12202,12 @@
       </c>
       <c r="L105" s="2" t="inlineStr">
         <is>
-          <t>9343</t>
+          <t>9706</t>
         </is>
       </c>
       <c r="M105" s="2" t="inlineStr">
         <is>
-          <t>24969</t>
+          <t>24937</t>
         </is>
       </c>
       <c r="N105" s="2" t="inlineStr">
@@ -12217,12 +12217,12 @@
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="P105" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="Q105" s="2" t="inlineStr">
@@ -12237,12 +12237,12 @@
       </c>
       <c r="S105" s="2" t="inlineStr">
         <is>
-          <t>18204</t>
+          <t>17820</t>
         </is>
       </c>
       <c r="T105" s="2" t="inlineStr">
         <is>
-          <t>36128</t>
+          <t>36001</t>
         </is>
       </c>
       <c r="U105" s="2" t="inlineStr">
@@ -12252,12 +12252,12 @@
       </c>
       <c r="V105" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="W105" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>12,9%</t>
         </is>
       </c>
     </row>
@@ -12320,7 +12320,7 @@
       </c>
       <c r="M106" s="2" t="inlineStr">
         <is>
-          <t>7092</t>
+          <t>6979</t>
         </is>
       </c>
       <c r="N106" s="2" t="inlineStr">
@@ -12335,7 +12335,7 @@
       </c>
       <c r="P106" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="Q106" s="2" t="inlineStr">
@@ -12355,7 +12355,7 @@
       </c>
       <c r="T106" s="2" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>6328</t>
         </is>
       </c>
       <c r="U106" s="2" t="inlineStr">
@@ -12370,7 +12370,7 @@
       </c>
       <c r="W106" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,27%</t>
         </is>
       </c>
     </row>
@@ -12433,7 +12433,7 @@
       </c>
       <c r="M107" s="2" t="inlineStr">
         <is>
-          <t>5133</t>
+          <t>5702</t>
         </is>
       </c>
       <c r="N107" s="2" t="inlineStr">
@@ -12448,7 +12448,7 @@
       </c>
       <c r="P107" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="Q107" s="2" t="inlineStr">
@@ -12468,7 +12468,7 @@
       </c>
       <c r="T107" s="2" t="inlineStr">
         <is>
-          <t>5262</t>
+          <t>4935</t>
         </is>
       </c>
       <c r="U107" s="2" t="inlineStr">
@@ -12483,7 +12483,7 @@
       </c>
       <c r="W107" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,77%</t>
         </is>
       </c>
     </row>
@@ -12741,7 +12741,7 @@
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>4793</t>
+          <t>4914</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
@@ -12756,7 +12756,7 @@
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="J110" s="2" t="inlineStr">
@@ -12776,7 +12776,7 @@
       </c>
       <c r="M110" s="2" t="inlineStr">
         <is>
-          <t>4616</t>
+          <t>4720</t>
         </is>
       </c>
       <c r="N110" s="2" t="inlineStr">
@@ -12791,7 +12791,7 @@
       </c>
       <c r="P110" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="Q110" s="2" t="inlineStr">
@@ -12806,12 +12806,12 @@
       </c>
       <c r="S110" s="2" t="inlineStr">
         <is>
-          <t>694</t>
+          <t>351</t>
         </is>
       </c>
       <c r="T110" s="2" t="inlineStr">
         <is>
-          <t>5780</t>
+          <t>5910</t>
         </is>
       </c>
       <c r="U110" s="2" t="inlineStr">
@@ -12821,12 +12821,12 @@
       </c>
       <c r="V110" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="W110" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,05%</t>
         </is>
       </c>
     </row>
@@ -12849,12 +12849,12 @@
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>2768</t>
+          <t>2748</t>
         </is>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>11270</t>
+          <t>11080</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
@@ -12864,12 +12864,12 @@
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="I111" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="J111" s="2" t="inlineStr">
@@ -12884,12 +12884,12 @@
       </c>
       <c r="L111" s="2" t="inlineStr">
         <is>
-          <t>9717</t>
+          <t>9591</t>
         </is>
       </c>
       <c r="M111" s="2" t="inlineStr">
         <is>
-          <t>22957</t>
+          <t>22296</t>
         </is>
       </c>
       <c r="N111" s="2" t="inlineStr">
@@ -12899,12 +12899,12 @@
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="P111" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="Q111" s="2" t="inlineStr">
@@ -12919,12 +12919,12 @@
       </c>
       <c r="S111" s="2" t="inlineStr">
         <is>
-          <t>14954</t>
+          <t>14206</t>
         </is>
       </c>
       <c r="T111" s="2" t="inlineStr">
         <is>
-          <t>29814</t>
+          <t>30268</t>
         </is>
       </c>
       <c r="U111" s="2" t="inlineStr">
@@ -12934,12 +12934,12 @@
       </c>
       <c r="V111" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="W111" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,49%</t>
         </is>
       </c>
     </row>
@@ -12962,12 +12962,12 @@
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>3384</t>
+          <t>3444</t>
         </is>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>12341</t>
+          <t>12291</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="I112" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="J112" s="2" t="inlineStr">
@@ -12997,12 +12997,12 @@
       </c>
       <c r="L112" s="2" t="inlineStr">
         <is>
-          <t>3817</t>
+          <t>3767</t>
         </is>
       </c>
       <c r="M112" s="2" t="inlineStr">
         <is>
-          <t>12873</t>
+          <t>13181</t>
         </is>
       </c>
       <c r="N112" s="2" t="inlineStr">
@@ -13012,12 +13012,12 @@
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="P112" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="Q112" s="2" t="inlineStr">
@@ -13032,12 +13032,12 @@
       </c>
       <c r="S112" s="2" t="inlineStr">
         <is>
-          <t>9316</t>
+          <t>9134</t>
         </is>
       </c>
       <c r="T112" s="2" t="inlineStr">
         <is>
-          <t>21620</t>
+          <t>22041</t>
         </is>
       </c>
       <c r="U112" s="2" t="inlineStr">
@@ -13047,12 +13047,12 @@
       </c>
       <c r="V112" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="W112" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,64%</t>
         </is>
       </c>
     </row>
@@ -13075,12 +13075,12 @@
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>393</t>
+          <t>379</t>
         </is>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>5667</t>
+          <t>4647</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
@@ -13090,12 +13090,12 @@
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="I113" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="J113" s="2" t="inlineStr">
@@ -13110,12 +13110,12 @@
       </c>
       <c r="L113" s="2" t="inlineStr">
         <is>
-          <t>889</t>
+          <t>883</t>
         </is>
       </c>
       <c r="M113" s="2" t="inlineStr">
         <is>
-          <t>7351</t>
+          <t>7250</t>
         </is>
       </c>
       <c r="N113" s="2" t="inlineStr">
@@ -13125,12 +13125,12 @@
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P113" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="Q113" s="2" t="inlineStr">
@@ -13145,12 +13145,12 @@
       </c>
       <c r="S113" s="2" t="inlineStr">
         <is>
-          <t>1855</t>
+          <t>1785</t>
         </is>
       </c>
       <c r="T113" s="2" t="inlineStr">
         <is>
-          <t>9388</t>
+          <t>9595</t>
         </is>
       </c>
       <c r="U113" s="2" t="inlineStr">
@@ -13160,12 +13160,12 @@
       </c>
       <c r="V113" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W113" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,33%</t>
         </is>
       </c>
     </row>
@@ -13228,7 +13228,7 @@
       </c>
       <c r="M114" s="2" t="inlineStr">
         <is>
-          <t>5019</t>
+          <t>4641</t>
         </is>
       </c>
       <c r="N114" s="2" t="inlineStr">
@@ -13243,7 +13243,7 @@
       </c>
       <c r="P114" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="Q114" s="2" t="inlineStr">
@@ -13263,7 +13263,7 @@
       </c>
       <c r="T114" s="2" t="inlineStr">
         <is>
-          <t>5522</t>
+          <t>4951</t>
         </is>
       </c>
       <c r="U114" s="2" t="inlineStr">
@@ -13278,7 +13278,7 @@
       </c>
       <c r="W114" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,72%</t>
         </is>
       </c>
     </row>
@@ -13301,12 +13301,12 @@
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>25445</t>
+          <t>25043</t>
         </is>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t>43117</t>
+          <t>42498</t>
         </is>
       </c>
       <c r="G115" s="2" t="inlineStr">
@@ -13316,12 +13316,12 @@
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="I115" s="2" t="inlineStr">
         <is>
-          <t>32,76%</t>
+          <t>32,29%</t>
         </is>
       </c>
       <c r="J115" s="2" t="inlineStr">
@@ -13336,12 +13336,12 @@
       </c>
       <c r="L115" s="2" t="inlineStr">
         <is>
-          <t>22477</t>
+          <t>21956</t>
         </is>
       </c>
       <c r="M115" s="2" t="inlineStr">
         <is>
-          <t>41050</t>
+          <t>40721</t>
         </is>
       </c>
       <c r="N115" s="2" t="inlineStr">
@@ -13351,12 +13351,12 @@
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="P115" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>25,97%</t>
         </is>
       </c>
       <c r="Q115" s="2" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="S115" s="2" t="inlineStr">
         <is>
-          <t>51549</t>
+          <t>53791</t>
         </is>
       </c>
       <c r="T115" s="2" t="inlineStr">
         <is>
-          <t>78413</t>
+          <t>78288</t>
         </is>
       </c>
       <c r="U115" s="2" t="inlineStr">
@@ -13386,12 +13386,12 @@
       </c>
       <c r="V115" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="W115" s="2" t="inlineStr">
         <is>
-          <t>27,19%</t>
+          <t>27,14%</t>
         </is>
       </c>
     </row>
@@ -13414,12 +13414,12 @@
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>6811</t>
+          <t>6969</t>
         </is>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>18377</t>
+          <t>18449</t>
         </is>
       </c>
       <c r="G116" s="2" t="inlineStr">
@@ -13429,12 +13429,12 @@
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="I116" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="J116" s="2" t="inlineStr">
@@ -13449,12 +13449,12 @@
       </c>
       <c r="L116" s="2" t="inlineStr">
         <is>
-          <t>6691</t>
+          <t>6625</t>
         </is>
       </c>
       <c r="M116" s="2" t="inlineStr">
         <is>
-          <t>17668</t>
+          <t>18399</t>
         </is>
       </c>
       <c r="N116" s="2" t="inlineStr">
@@ -13464,12 +13464,12 @@
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="P116" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="Q116" s="2" t="inlineStr">
@@ -13484,12 +13484,12 @@
       </c>
       <c r="S116" s="2" t="inlineStr">
         <is>
-          <t>16081</t>
+          <t>15586</t>
         </is>
       </c>
       <c r="T116" s="2" t="inlineStr">
         <is>
-          <t>31297</t>
+          <t>31331</t>
         </is>
       </c>
       <c r="U116" s="2" t="inlineStr">
@@ -13499,12 +13499,12 @@
       </c>
       <c r="V116" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="W116" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>10,86%</t>
         </is>
       </c>
     </row>
@@ -13527,12 +13527,12 @@
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>2275</t>
         </is>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t>12331</t>
+          <t>12122</t>
         </is>
       </c>
       <c r="G117" s="2" t="inlineStr">
@@ -13542,12 +13542,12 @@
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="I117" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="J117" s="2" t="inlineStr">
@@ -13562,12 +13562,12 @@
       </c>
       <c r="L117" s="2" t="inlineStr">
         <is>
-          <t>3385</t>
+          <t>3233</t>
         </is>
       </c>
       <c r="M117" s="2" t="inlineStr">
         <is>
-          <t>12708</t>
+          <t>12259</t>
         </is>
       </c>
       <c r="N117" s="2" t="inlineStr">
@@ -13577,12 +13577,12 @@
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="P117" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="Q117" s="2" t="inlineStr">
@@ -13597,12 +13597,12 @@
       </c>
       <c r="S117" s="2" t="inlineStr">
         <is>
-          <t>7021</t>
+          <t>7064</t>
         </is>
       </c>
       <c r="T117" s="2" t="inlineStr">
         <is>
-          <t>19900</t>
+          <t>20779</t>
         </is>
       </c>
       <c r="U117" s="2" t="inlineStr">
@@ -13612,12 +13612,12 @@
       </c>
       <c r="V117" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="W117" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>7,2%</t>
         </is>
       </c>
     </row>
@@ -13640,12 +13640,12 @@
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>11945</t>
+          <t>11584</t>
         </is>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>24390</t>
+          <t>25957</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr">
@@ -13655,12 +13655,12 @@
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="I118" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>19,72%</t>
         </is>
       </c>
       <c r="J118" s="2" t="inlineStr">
@@ -13675,12 +13675,12 @@
       </c>
       <c r="L118" s="2" t="inlineStr">
         <is>
-          <t>17501</t>
+          <t>17191</t>
         </is>
       </c>
       <c r="M118" s="2" t="inlineStr">
         <is>
-          <t>33936</t>
+          <t>33838</t>
         </is>
       </c>
       <c r="N118" s="2" t="inlineStr">
@@ -13690,12 +13690,12 @@
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="P118" s="2" t="inlineStr">
         <is>
-          <t>21,64%</t>
+          <t>21,58%</t>
         </is>
       </c>
       <c r="Q118" s="2" t="inlineStr">
@@ -13710,12 +13710,12 @@
       </c>
       <c r="S118" s="2" t="inlineStr">
         <is>
-          <t>33133</t>
+          <t>32885</t>
         </is>
       </c>
       <c r="T118" s="2" t="inlineStr">
         <is>
-          <t>53492</t>
+          <t>52509</t>
         </is>
       </c>
       <c r="U118" s="2" t="inlineStr">
@@ -13725,12 +13725,12 @@
       </c>
       <c r="V118" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="W118" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>18,21%</t>
         </is>
       </c>
     </row>
@@ -13753,12 +13753,12 @@
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>24202</t>
+          <t>23936</t>
         </is>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>40562</t>
+          <t>41753</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
@@ -13768,12 +13768,12 @@
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,19%</t>
         </is>
       </c>
       <c r="I119" s="2" t="inlineStr">
         <is>
-          <t>30,82%</t>
+          <t>31,72%</t>
         </is>
       </c>
       <c r="J119" s="2" t="inlineStr">
@@ -13788,12 +13788,12 @@
       </c>
       <c r="L119" s="2" t="inlineStr">
         <is>
-          <t>31977</t>
+          <t>31096</t>
         </is>
       </c>
       <c r="M119" s="2" t="inlineStr">
         <is>
-          <t>50979</t>
+          <t>51999</t>
         </is>
       </c>
       <c r="N119" s="2" t="inlineStr">
@@ -13803,12 +13803,12 @@
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>19,83%</t>
         </is>
       </c>
       <c r="P119" s="2" t="inlineStr">
         <is>
-          <t>32,51%</t>
+          <t>33,16%</t>
         </is>
       </c>
       <c r="Q119" s="2" t="inlineStr">
@@ -13823,12 +13823,12 @@
       </c>
       <c r="S119" s="2" t="inlineStr">
         <is>
-          <t>60059</t>
+          <t>59749</t>
         </is>
       </c>
       <c r="T119" s="2" t="inlineStr">
         <is>
-          <t>85285</t>
+          <t>86176</t>
         </is>
       </c>
       <c r="U119" s="2" t="inlineStr">
@@ -13838,12 +13838,12 @@
       </c>
       <c r="V119" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="W119" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>29,88%</t>
         </is>
       </c>
     </row>
@@ -13866,12 +13866,12 @@
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>6568</t>
+          <t>6362</t>
         </is>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>17364</t>
+          <t>17088</t>
         </is>
       </c>
       <c r="G120" s="2" t="inlineStr">
@@ -13881,12 +13881,12 @@
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="I120" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="J120" s="2" t="inlineStr">
@@ -13901,12 +13901,12 @@
       </c>
       <c r="L120" s="2" t="inlineStr">
         <is>
-          <t>8091</t>
+          <t>8633</t>
         </is>
       </c>
       <c r="M120" s="2" t="inlineStr">
         <is>
-          <t>20898</t>
+          <t>21217</t>
         </is>
       </c>
       <c r="N120" s="2" t="inlineStr">
@@ -13916,12 +13916,12 @@
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="P120" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="Q120" s="2" t="inlineStr">
@@ -13936,12 +13936,12 @@
       </c>
       <c r="S120" s="2" t="inlineStr">
         <is>
-          <t>17683</t>
+          <t>17708</t>
         </is>
       </c>
       <c r="T120" s="2" t="inlineStr">
         <is>
-          <t>34120</t>
+          <t>34011</t>
         </is>
       </c>
       <c r="U120" s="2" t="inlineStr">
@@ -13951,12 +13951,12 @@
       </c>
       <c r="V120" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="W120" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>11,79%</t>
         </is>
       </c>
     </row>
@@ -13979,12 +13979,12 @@
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>1869</t>
+          <t>1972</t>
         </is>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>10436</t>
+          <t>9959</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr">
@@ -13994,12 +13994,12 @@
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="I121" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="J121" s="2" t="inlineStr">
@@ -14019,7 +14019,7 @@
       </c>
       <c r="M121" s="2" t="inlineStr">
         <is>
-          <t>2093</t>
+          <t>2502</t>
         </is>
       </c>
       <c r="N121" s="2" t="inlineStr">
@@ -14034,7 +14034,7 @@
       </c>
       <c r="P121" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="Q121" s="2" t="inlineStr">
@@ -14049,12 +14049,12 @@
       </c>
       <c r="S121" s="2" t="inlineStr">
         <is>
-          <t>2194</t>
+          <t>2440</t>
         </is>
       </c>
       <c r="T121" s="2" t="inlineStr">
         <is>
-          <t>11450</t>
+          <t>11823</t>
         </is>
       </c>
       <c r="U121" s="2" t="inlineStr">
@@ -14064,12 +14064,12 @@
       </c>
       <c r="V121" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W121" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,1%</t>
         </is>
       </c>
     </row>
@@ -14327,7 +14327,7 @@
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t>2582</t>
+          <t>2477</t>
         </is>
       </c>
       <c r="G124" s="2" t="inlineStr">
@@ -14342,7 +14342,7 @@
       </c>
       <c r="I124" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="J124" s="2" t="inlineStr">
@@ -14362,7 +14362,7 @@
       </c>
       <c r="M124" s="2" t="inlineStr">
         <is>
-          <t>4361</t>
+          <t>4863</t>
         </is>
       </c>
       <c r="N124" s="2" t="inlineStr">
@@ -14377,7 +14377,7 @@
       </c>
       <c r="P124" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="Q124" s="2" t="inlineStr">
@@ -14397,7 +14397,7 @@
       </c>
       <c r="T124" s="2" t="inlineStr">
         <is>
-          <t>5377</t>
+          <t>5112</t>
         </is>
       </c>
       <c r="U124" s="2" t="inlineStr">
@@ -14412,7 +14412,7 @@
       </c>
       <c r="W124" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,36%</t>
         </is>
       </c>
     </row>
@@ -14435,12 +14435,12 @@
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>1161</t>
+          <t>1325</t>
         </is>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t>7525</t>
+          <t>7493</t>
         </is>
       </c>
       <c r="G125" s="2" t="inlineStr">
@@ -14450,7 +14450,7 @@
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="I125" s="2" t="inlineStr">
@@ -14470,12 +14470,12 @@
       </c>
       <c r="L125" s="2" t="inlineStr">
         <is>
-          <t>1169</t>
+          <t>1244</t>
         </is>
       </c>
       <c r="M125" s="2" t="inlineStr">
         <is>
-          <t>9088</t>
+          <t>8683</t>
         </is>
       </c>
       <c r="N125" s="2" t="inlineStr">
@@ -14485,12 +14485,12 @@
       </c>
       <c r="O125" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="P125" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="Q125" s="2" t="inlineStr">
@@ -14505,12 +14505,12 @@
       </c>
       <c r="S125" s="2" t="inlineStr">
         <is>
-          <t>3599</t>
+          <t>3562</t>
         </is>
       </c>
       <c r="T125" s="2" t="inlineStr">
         <is>
-          <t>12874</t>
+          <t>13355</t>
         </is>
       </c>
       <c r="U125" s="2" t="inlineStr">
@@ -14525,7 +14525,7 @@
       </c>
       <c r="W125" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,94%</t>
         </is>
       </c>
     </row>
@@ -14548,12 +14548,12 @@
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>64303</t>
+          <t>63361</t>
         </is>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>95848</t>
+          <t>94175</t>
         </is>
       </c>
       <c r="G126" s="2" t="inlineStr">
@@ -14563,12 +14563,12 @@
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="I126" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="J126" s="2" t="inlineStr">
@@ -14583,12 +14583,12 @@
       </c>
       <c r="L126" s="2" t="inlineStr">
         <is>
-          <t>85977</t>
+          <t>84300</t>
         </is>
       </c>
       <c r="M126" s="2" t="inlineStr">
         <is>
-          <t>126235</t>
+          <t>123240</t>
         </is>
       </c>
       <c r="N126" s="2" t="inlineStr">
@@ -14598,12 +14598,12 @@
       </c>
       <c r="O126" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="P126" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="Q126" s="2" t="inlineStr">
@@ -14618,12 +14618,12 @@
       </c>
       <c r="S126" s="2" t="inlineStr">
         <is>
-          <t>157042</t>
+          <t>158994</t>
         </is>
       </c>
       <c r="T126" s="2" t="inlineStr">
         <is>
-          <t>206400</t>
+          <t>207034</t>
         </is>
       </c>
       <c r="U126" s="2" t="inlineStr">
@@ -14633,12 +14633,12 @@
       </c>
       <c r="V126" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="W126" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,51%</t>
         </is>
       </c>
     </row>
@@ -14661,12 +14661,12 @@
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>41326</t>
+          <t>40614</t>
         </is>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
-          <t>66081</t>
+          <t>65489</t>
         </is>
       </c>
       <c r="G127" s="2" t="inlineStr">
@@ -14676,12 +14676,12 @@
       </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="I127" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="J127" s="2" t="inlineStr">
@@ -14696,12 +14696,12 @@
       </c>
       <c r="L127" s="2" t="inlineStr">
         <is>
-          <t>46768</t>
+          <t>46001</t>
         </is>
       </c>
       <c r="M127" s="2" t="inlineStr">
         <is>
-          <t>74403</t>
+          <t>74949</t>
         </is>
       </c>
       <c r="N127" s="2" t="inlineStr">
@@ -14711,12 +14711,12 @@
       </c>
       <c r="O127" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="P127" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="Q127" s="2" t="inlineStr">
@@ -14731,12 +14731,12 @@
       </c>
       <c r="S127" s="2" t="inlineStr">
         <is>
-          <t>94889</t>
+          <t>95445</t>
         </is>
       </c>
       <c r="T127" s="2" t="inlineStr">
         <is>
-          <t>131304</t>
+          <t>130783</t>
         </is>
       </c>
       <c r="U127" s="2" t="inlineStr">
@@ -14746,12 +14746,12 @@
       </c>
       <c r="V127" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="W127" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,17%</t>
         </is>
       </c>
     </row>
@@ -14774,12 +14774,12 @@
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>6945</t>
+          <t>6555</t>
         </is>
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
-          <t>17458</t>
+          <t>16295</t>
         </is>
       </c>
       <c r="G128" s="2" t="inlineStr">
@@ -14789,12 +14789,12 @@
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I128" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="J128" s="2" t="inlineStr">
@@ -14809,12 +14809,12 @@
       </c>
       <c r="L128" s="2" t="inlineStr">
         <is>
-          <t>8854</t>
+          <t>9083</t>
         </is>
       </c>
       <c r="M128" s="2" t="inlineStr">
         <is>
-          <t>23196</t>
+          <t>23252</t>
         </is>
       </c>
       <c r="N128" s="2" t="inlineStr">
@@ -14824,12 +14824,12 @@
       </c>
       <c r="O128" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="P128" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="Q128" s="2" t="inlineStr">
@@ -14844,12 +14844,12 @@
       </c>
       <c r="S128" s="2" t="inlineStr">
         <is>
-          <t>18633</t>
+          <t>19529</t>
         </is>
       </c>
       <c r="T128" s="2" t="inlineStr">
         <is>
-          <t>36972</t>
+          <t>36168</t>
         </is>
       </c>
       <c r="U128" s="2" t="inlineStr">
@@ -14859,12 +14859,12 @@
       </c>
       <c r="V128" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="W128" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,54%</t>
         </is>
       </c>
     </row>
@@ -14892,7 +14892,7 @@
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>2853</t>
         </is>
       </c>
       <c r="G129" s="2" t="inlineStr">
@@ -14907,7 +14907,7 @@
       </c>
       <c r="I129" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="J129" s="2" t="inlineStr">
@@ -14922,12 +14922,12 @@
       </c>
       <c r="L129" s="2" t="inlineStr">
         <is>
-          <t>2638</t>
+          <t>2474</t>
         </is>
       </c>
       <c r="M129" s="2" t="inlineStr">
         <is>
-          <t>10593</t>
+          <t>10019</t>
         </is>
       </c>
       <c r="N129" s="2" t="inlineStr">
@@ -14937,12 +14937,12 @@
       </c>
       <c r="O129" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="P129" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="Q129" s="2" t="inlineStr">
@@ -14957,12 +14957,12 @@
       </c>
       <c r="S129" s="2" t="inlineStr">
         <is>
-          <t>3297</t>
+          <t>3331</t>
         </is>
       </c>
       <c r="T129" s="2" t="inlineStr">
         <is>
-          <t>11672</t>
+          <t>11694</t>
         </is>
       </c>
       <c r="U129" s="2" t="inlineStr">
@@ -15000,12 +15000,12 @@
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>77009</t>
+          <t>75975</t>
         </is>
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>111011</t>
+          <t>110896</t>
         </is>
       </c>
       <c r="G130" s="2" t="inlineStr">
@@ -15015,12 +15015,12 @@
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="I130" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="J130" s="2" t="inlineStr">
@@ -15035,12 +15035,12 @@
       </c>
       <c r="L130" s="2" t="inlineStr">
         <is>
-          <t>70363</t>
+          <t>69582</t>
         </is>
       </c>
       <c r="M130" s="2" t="inlineStr">
         <is>
-          <t>104241</t>
+          <t>104907</t>
         </is>
       </c>
       <c r="N130" s="2" t="inlineStr">
@@ -15050,12 +15050,12 @@
       </c>
       <c r="O130" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="P130" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="Q130" s="2" t="inlineStr">
@@ -15070,12 +15070,12 @@
       </c>
       <c r="S130" s="2" t="inlineStr">
         <is>
-          <t>154625</t>
+          <t>155580</t>
         </is>
       </c>
       <c r="T130" s="2" t="inlineStr">
         <is>
-          <t>203407</t>
+          <t>202584</t>
         </is>
       </c>
       <c r="U130" s="2" t="inlineStr">
@@ -15085,12 +15085,12 @@
       </c>
       <c r="V130" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="W130" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,2%</t>
         </is>
       </c>
     </row>
@@ -15113,12 +15113,12 @@
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>63604</t>
+          <t>64875</t>
         </is>
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
-          <t>96272</t>
+          <t>96169</t>
         </is>
       </c>
       <c r="G131" s="2" t="inlineStr">
@@ -15128,12 +15128,12 @@
       </c>
       <c r="H131" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="I131" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="J131" s="2" t="inlineStr">
@@ -15148,12 +15148,12 @@
       </c>
       <c r="L131" s="2" t="inlineStr">
         <is>
-          <t>60125</t>
+          <t>59276</t>
         </is>
       </c>
       <c r="M131" s="2" t="inlineStr">
         <is>
-          <t>92968</t>
+          <t>90632</t>
         </is>
       </c>
       <c r="N131" s="2" t="inlineStr">
@@ -15163,12 +15163,12 @@
       </c>
       <c r="O131" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="P131" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="Q131" s="2" t="inlineStr">
@@ -15183,12 +15183,12 @@
       </c>
       <c r="S131" s="2" t="inlineStr">
         <is>
-          <t>131214</t>
+          <t>132047</t>
         </is>
       </c>
       <c r="T131" s="2" t="inlineStr">
         <is>
-          <t>177486</t>
+          <t>178201</t>
         </is>
       </c>
       <c r="U131" s="2" t="inlineStr">
@@ -15198,12 +15198,12 @@
       </c>
       <c r="V131" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="W131" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>12,49%</t>
         </is>
       </c>
     </row>
@@ -15226,12 +15226,12 @@
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>29735</t>
+          <t>31773</t>
         </is>
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
-          <t>51794</t>
+          <t>52611</t>
         </is>
       </c>
       <c r="G132" s="2" t="inlineStr">
@@ -15241,12 +15241,12 @@
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="I132" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="J132" s="2" t="inlineStr">
@@ -15261,12 +15261,12 @@
       </c>
       <c r="L132" s="2" t="inlineStr">
         <is>
-          <t>54608</t>
+          <t>53631</t>
         </is>
       </c>
       <c r="M132" s="2" t="inlineStr">
         <is>
-          <t>84434</t>
+          <t>83478</t>
         </is>
       </c>
       <c r="N132" s="2" t="inlineStr">
@@ -15276,12 +15276,12 @@
       </c>
       <c r="O132" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="P132" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="Q132" s="2" t="inlineStr">
@@ -15296,12 +15296,12 @@
       </c>
       <c r="S132" s="2" t="inlineStr">
         <is>
-          <t>91750</t>
+          <t>90496</t>
         </is>
       </c>
       <c r="T132" s="2" t="inlineStr">
         <is>
-          <t>127591</t>
+          <t>128065</t>
         </is>
       </c>
       <c r="U132" s="2" t="inlineStr">
@@ -15311,12 +15311,12 @@
       </c>
       <c r="V132" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="W132" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,98%</t>
         </is>
       </c>
     </row>
@@ -15339,12 +15339,12 @@
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>92745</t>
+          <t>93404</t>
         </is>
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
-          <t>195311</t>
+          <t>194431</t>
         </is>
       </c>
       <c r="G133" s="2" t="inlineStr">
@@ -15354,12 +15354,12 @@
       </c>
       <c r="H133" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="I133" s="2" t="inlineStr">
         <is>
-          <t>29,38%</t>
+          <t>29,25%</t>
         </is>
       </c>
       <c r="J133" s="2" t="inlineStr">
@@ -15374,12 +15374,12 @@
       </c>
       <c r="L133" s="2" t="inlineStr">
         <is>
-          <t>93957</t>
+          <t>94479</t>
         </is>
       </c>
       <c r="M133" s="2" t="inlineStr">
         <is>
-          <t>151219</t>
+          <t>150271</t>
         </is>
       </c>
       <c r="N133" s="2" t="inlineStr">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="O133" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="P133" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>19,72%</t>
         </is>
       </c>
       <c r="Q133" s="2" t="inlineStr">
@@ -15409,12 +15409,12 @@
       </c>
       <c r="S133" s="2" t="inlineStr">
         <is>
-          <t>199766</t>
+          <t>201855</t>
         </is>
       </c>
       <c r="T133" s="2" t="inlineStr">
         <is>
-          <t>323799</t>
+          <t>308942</t>
         </is>
       </c>
       <c r="U133" s="2" t="inlineStr">
@@ -15424,12 +15424,12 @@
       </c>
       <c r="V133" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="W133" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>21,65%</t>
         </is>
       </c>
     </row>
@@ -15452,12 +15452,12 @@
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>99893</t>
+          <t>99613</t>
         </is>
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t>138091</t>
+          <t>138386</t>
         </is>
       </c>
       <c r="G134" s="2" t="inlineStr">
@@ -15467,12 +15467,12 @@
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="I134" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="J134" s="2" t="inlineStr">
@@ -15487,12 +15487,12 @@
       </c>
       <c r="L134" s="2" t="inlineStr">
         <is>
-          <t>138180</t>
+          <t>139247</t>
         </is>
       </c>
       <c r="M134" s="2" t="inlineStr">
         <is>
-          <t>183911</t>
+          <t>189863</t>
         </is>
       </c>
       <c r="N134" s="2" t="inlineStr">
@@ -15502,12 +15502,12 @@
       </c>
       <c r="O134" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="P134" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="Q134" s="2" t="inlineStr">
@@ -15522,12 +15522,12 @@
       </c>
       <c r="S134" s="2" t="inlineStr">
         <is>
-          <t>251117</t>
+          <t>251966</t>
         </is>
       </c>
       <c r="T134" s="2" t="inlineStr">
         <is>
-          <t>313341</t>
+          <t>311459</t>
         </is>
       </c>
       <c r="U134" s="2" t="inlineStr">
@@ -15537,12 +15537,12 @@
       </c>
       <c r="V134" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="W134" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>21,83%</t>
         </is>
       </c>
     </row>
@@ -15565,12 +15565,12 @@
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>36365</t>
+          <t>36402</t>
         </is>
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
-          <t>72500</t>
+          <t>73144</t>
         </is>
       </c>
       <c r="G135" s="2" t="inlineStr">
@@ -15580,12 +15580,12 @@
       </c>
       <c r="H135" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="I135" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="J135" s="2" t="inlineStr">
@@ -15600,12 +15600,12 @@
       </c>
       <c r="L135" s="2" t="inlineStr">
         <is>
-          <t>46947</t>
+          <t>45709</t>
         </is>
       </c>
       <c r="M135" s="2" t="inlineStr">
         <is>
-          <t>73989</t>
+          <t>75013</t>
         </is>
       </c>
       <c r="N135" s="2" t="inlineStr">
@@ -15615,12 +15615,12 @@
       </c>
       <c r="O135" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="P135" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="Q135" s="2" t="inlineStr">
@@ -15635,12 +15635,12 @@
       </c>
       <c r="S135" s="2" t="inlineStr">
         <is>
-          <t>88996</t>
+          <t>88388</t>
         </is>
       </c>
       <c r="T135" s="2" t="inlineStr">
         <is>
-          <t>133332</t>
+          <t>136719</t>
         </is>
       </c>
       <c r="U135" s="2" t="inlineStr">
@@ -15650,12 +15650,12 @@
       </c>
       <c r="V135" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="W135" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,58%</t>
         </is>
       </c>
     </row>
@@ -15678,12 +15678,12 @@
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>5982</t>
+          <t>6070</t>
         </is>
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
-          <t>16878</t>
+          <t>17380</t>
         </is>
       </c>
       <c r="G136" s="2" t="inlineStr">
@@ -15693,12 +15693,12 @@
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I136" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="J136" s="2" t="inlineStr">
@@ -15713,12 +15713,12 @@
       </c>
       <c r="L136" s="2" t="inlineStr">
         <is>
-          <t>5387</t>
+          <t>5830</t>
         </is>
       </c>
       <c r="M136" s="2" t="inlineStr">
         <is>
-          <t>18568</t>
+          <t>18478</t>
         </is>
       </c>
       <c r="N136" s="2" t="inlineStr">
@@ -15728,12 +15728,12 @@
       </c>
       <c r="O136" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P136" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="Q136" s="2" t="inlineStr">
@@ -15748,12 +15748,12 @@
       </c>
       <c r="S136" s="2" t="inlineStr">
         <is>
-          <t>13912</t>
+          <t>14174</t>
         </is>
       </c>
       <c r="T136" s="2" t="inlineStr">
         <is>
-          <t>30894</t>
+          <t>32278</t>
         </is>
       </c>
       <c r="U136" s="2" t="inlineStr">
@@ -15763,12 +15763,12 @@
       </c>
       <c r="V136" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="W136" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,26%</t>
         </is>
       </c>
     </row>
@@ -15791,12 +15791,12 @@
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>496</t>
+          <t>483</t>
         </is>
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
-          <t>5544</t>
+          <t>5258</t>
         </is>
       </c>
       <c r="G137" s="2" t="inlineStr">
@@ -15811,7 +15811,7 @@
       </c>
       <c r="I137" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="J137" s="2" t="inlineStr">
@@ -15826,12 +15826,12 @@
       </c>
       <c r="L137" s="2" t="inlineStr">
         <is>
-          <t>1206</t>
+          <t>1165</t>
         </is>
       </c>
       <c r="M137" s="2" t="inlineStr">
         <is>
-          <t>7591</t>
+          <t>7752</t>
         </is>
       </c>
       <c r="N137" s="2" t="inlineStr">
@@ -15841,12 +15841,12 @@
       </c>
       <c r="O137" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="P137" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="Q137" s="2" t="inlineStr">
@@ -15861,12 +15861,12 @@
       </c>
       <c r="S137" s="2" t="inlineStr">
         <is>
-          <t>2554</t>
+          <t>2560</t>
         </is>
       </c>
       <c r="T137" s="2" t="inlineStr">
         <is>
-          <t>10499</t>
+          <t>10331</t>
         </is>
       </c>
       <c r="U137" s="2" t="inlineStr">
@@ -15881,7 +15881,7 @@
       </c>
       <c r="W137" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,72%</t>
         </is>
       </c>
     </row>
